--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:14</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,10 +493,10 @@
         <v>15.72</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>94.99</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>79.27</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         <v>47.83</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>53.07</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="5">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:41</t>
+    <t xml:space="preserve">2026-10-05 04:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -507,7 +507,7 @@
         <v>-2.8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>83.66</v>
+        <v>83.67</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>86.47</v>
@@ -524,7 +524,7 @@
         <v>47.83</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>53.06</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="5">
